--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-23).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-23).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-168</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>R$ 744.496,65</t>
-  </si>
-  <si>
-    <t>R$ 4.182,57
-R$ 4.250,44</t>
-  </si>
-  <si>
-    <t>(9.7%)
-(8.3%)</t>
-  </si>
-  <si>
-    <t>46.2</t>
+174</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 770.566,92</t>
+  </si>
+  <si>
+    <t>R$ 4.187,86
+R$ 4.253,70</t>
+  </si>
+  <si>
+    <t>(10.0%)
+(8.5%)</t>
+  </si>
+  <si>
+    <t>46.3</t>
   </si>
   <si>
     <t>(14.7%)</t>
   </si>
   <si>
-    <t>409.3%</t>
-  </si>
-  <si>
-    <t>364.5%</t>
+    <t>396.2%</t>
+  </si>
+  <si>
+    <t>351.7%</t>
   </si>
   <si>
     <t>3.7%</t>
@@ -950,10 +950,10 @@
     <t>25.7</t>
   </si>
   <si>
-    <t>74.9%</t>
-  </si>
-  <si>
-    <t>7.6%</t>
+    <t>74.7%</t>
+  </si>
+  <si>
+    <t>7.7%</t>
   </si>
   <si>
     <t>4.8</t>
@@ -971,7 +971,7 @@
     <t>76.9%</t>
   </si>
   <si>
-    <t>-R$ 24.365,35</t>
+    <t>-R$ 26.321,95</t>
   </si>
   <si>
     <t>2.95</t>
@@ -2737,10 +2737,10 @@
         <v>0.034482758620689724</v>
       </c>
       <c r="T11" s="6">
-        <v>2.3827883791685451</v>
+        <v>2.3827535914677367</v>
       </c>
       <c r="U11" s="6">
-        <v>-0.072604366726143968</v>
+        <v>-0.072639154426952346</v>
       </c>
       <c r="V11" s="6">
         <v>0.028078240438093115</v>
@@ -2947,7 +2947,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2983,25 +2983,61 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="O13" s="5">
+        <v>6863.7600000000002</v>
+      </c>
+      <c r="P13" s="5">
+        <v>6863.7600000000002</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>0.037185237122375092</v>
+      </c>
+      <c r="R13" s="7">
+        <v>75</v>
+      </c>
+      <c r="S13" s="6">
+        <v>-0.07407407407407407</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.32925333927759709</v>
+      </c>
+      <c r="U13" s="6">
+        <v>-0.0033034517523922746</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.029519505344009697</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.02659836591022996</v>
+      </c>
+      <c r="X13" s="8">
+        <v>29.552727272727275</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.5636363636363636</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.21818181818181817</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>6.1448202702702703</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>6.6303036363636361</v>
+      </c>
+      <c r="AC13" s="8">
+        <v>12.45303</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>19.405454545454546</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.63636363636363635</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>-92.400000000000006</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -6638,7 +6674,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6674,25 +6710,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>2882.3099999999999</v>
+      </c>
+      <c r="P42" s="5">
+        <v>2882.3099999999999</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.34812079049380984</v>
+      </c>
+      <c r="R42" s="7">
+        <v>36</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.25</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.35021805426897179</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.030373901488736463</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.07851879221874121</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.0078150858165846153</v>
+      </c>
+      <c r="X42" s="8">
+        <v>22.888887499999999</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>4.3122558823529413</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>3.2717391304347827</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>7.9196549999999997</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>14.653470833333332</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -7868,7 +7940,7 @@
         <v>19606</v>
       </c>
       <c r="B52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C52" s="4">
         <v>44</v>
@@ -7904,25 +7976,61 @@
       <c t="s" r="N52" s="4">
         <v>52</v>
       </c>
-      <c r="O52" s="5"/>
-      <c r="P52" s="5"/>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="7"/>
-      <c r="S52" s="6"/>
-      <c r="T52" s="6"/>
-      <c r="U52" s="6"/>
-      <c r="V52" s="6"/>
-      <c r="W52" s="6"/>
-      <c r="X52" s="8"/>
-      <c r="Y52" s="6"/>
-      <c r="Z52" s="6"/>
-      <c r="AA52" s="8"/>
-      <c r="AB52" s="8"/>
-      <c r="AC52" s="8"/>
-      <c r="AD52" s="8"/>
-      <c r="AE52" s="6"/>
+      <c r="O52" s="5">
+        <v>4573.1000000000004</v>
+      </c>
+      <c r="P52" s="5">
+        <v>4573.1000000000004</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>-0.48226165083936756</v>
+      </c>
+      <c r="R52" s="7">
+        <v>44</v>
+      </c>
+      <c r="S52" s="6">
+        <v>-0.51111111111111107</v>
+      </c>
+      <c r="T52" s="6">
+        <v>0</v>
+      </c>
+      <c r="U52" s="6">
+        <v>-0.35106164308674637</v>
+      </c>
+      <c r="V52" s="6">
+        <v>0.026355863637357591</v>
+      </c>
+      <c r="W52" s="6">
+        <v>0.0032643064879403468</v>
+      </c>
+      <c r="X52" s="8">
+        <v>25.550927777777776</v>
+      </c>
+      <c r="Y52" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="8">
+        <v>6.9405804347826088</v>
+      </c>
+      <c r="AB52" s="8">
+        <v>2.8858999999999999</v>
+      </c>
+      <c r="AC52" s="8">
+        <v>9.9665979999999994</v>
+      </c>
+      <c r="AD52" s="8">
+        <v>16.341666666666665</v>
+      </c>
+      <c r="AE52" s="6">
+        <v>0.88888888888888884</v>
+      </c>
       <c r="AF52" s="9"/>
-      <c r="AG52" s="5"/>
+      <c r="AG52" s="5">
+        <v>-1181.5</v>
+      </c>
       <c r="AH52" s="10">
         <v>1</v>
       </c>
@@ -8039,7 +8147,9 @@
       <c r="AB53" s="8">
         <v>3.2526870967741934</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>6.604838</v>
+      </c>
       <c r="AD53" s="8">
         <v>13.551612903225807</v>
       </c>
@@ -8612,7 +8722,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8648,25 +8758,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="O58" s="5">
+        <v>4574.1499999999996</v>
+      </c>
+      <c r="P58" s="5">
+        <v>4574.1499999999996</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.0042041712403950715</v>
+      </c>
+      <c r="R58" s="7">
+        <v>56</v>
+      </c>
+      <c r="S58" s="6">
+        <v>0.076923076923076872</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.24564207557688314</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.13351908004765914</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.010694445962637867</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.0079953652591191818</v>
+      </c>
+      <c r="X58" s="8">
+        <v>26.004470731707315</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.51219512195121952</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>2.974405357142857</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>7.2299999999999995</v>
+      </c>
+      <c r="AC58" s="8">
+        <v>10.373089</v>
+      </c>
+      <c r="AD58" s="8">
+        <v>17.039024390243902</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.75609756097560976</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-116.59999999999999</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -10100,7 +10246,7 @@
         <v>19648</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C70" s="4">
         <v>44</v>
@@ -10136,27 +10282,61 @@
       <c t="s" r="N70" s="4">
         <v>52</v>
       </c>
-      <c r="O70" s="5"/>
-      <c r="P70" s="5"/>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="7"/>
-      <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
-      <c r="V70" s="6"/>
-      <c r="W70" s="6"/>
-      <c r="X70" s="8"/>
-      <c r="Y70" s="6"/>
-      <c r="Z70" s="6"/>
-      <c r="AA70" s="8"/>
-      <c r="AB70" s="8"/>
+      <c r="O70" s="5">
+        <v>3936.3499999999999</v>
+      </c>
+      <c r="P70" s="5">
+        <v>3936.3499999999999</v>
+      </c>
+      <c r="Q70" s="6">
+        <v>0.085476425526282318</v>
+      </c>
+      <c r="R70" s="7">
+        <v>48</v>
+      </c>
+      <c r="S70" s="6">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="T70" s="6">
+        <v>0.40159866373671044</v>
+      </c>
+      <c r="U70" s="6">
+        <v>-0.015683844170360867</v>
+      </c>
+      <c r="V70" s="6">
+        <v>0.01834554854116123</v>
+      </c>
+      <c r="W70" s="6">
+        <v>0.0032859120759078844</v>
+      </c>
+      <c r="X70" s="8">
+        <v>27.590476190476188</v>
+      </c>
+      <c r="Y70" s="6">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="Z70" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA70" s="8">
+        <v>3.134313725490196</v>
+      </c>
+      <c r="AB70" s="8">
+        <v>10.778335</v>
+      </c>
       <c r="AC70" s="8">
         <v>14.072777</v>
       </c>
-      <c r="AD70" s="8"/>
-      <c r="AE70" s="6"/>
+      <c r="AD70" s="8">
+        <v>20.331747619047619</v>
+      </c>
+      <c r="AE70" s="6">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="AF70" s="9"/>
-      <c r="AG70" s="5"/>
+      <c r="AG70" s="5">
+        <v>21.100000000000001</v>
+      </c>
       <c r="AH70" s="10">
         <v>2</v>
       </c>
@@ -10882,7 +11062,9 @@
       <c r="AB76" s="8">
         <v>7.7333325581395345</v>
       </c>
-      <c r="AC76" s="8"/>
+      <c r="AC76" s="8">
+        <v>10.613702999999999</v>
+      </c>
       <c r="AD76" s="8">
         <v>19.081851111111114</v>
       </c>
@@ -20671,7 +20853,7 @@
         <v>0.025825338862412575</v>
       </c>
       <c r="W154" s="6">
-        <v>-0.022607744837119099</v>
+        <v>-0.023965257576695344</v>
       </c>
       <c r="X154" s="8">
         <v>21.39743846153846</v>
@@ -21447,7 +21629,7 @@
         <v>19868</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C161" s="4">
         <v>44</v>
@@ -21483,25 +21665,47 @@
       <c t="s" r="N161" s="4">
         <v>52</v>
       </c>
-      <c r="O161" s="5"/>
-      <c r="P161" s="5"/>
-      <c r="Q161" s="6"/>
-      <c r="R161" s="7"/>
-      <c r="S161" s="6"/>
-      <c r="T161" s="6"/>
-      <c r="U161" s="6"/>
-      <c r="V161" s="6"/>
-      <c r="W161" s="6"/>
+      <c r="O161" s="5">
+        <v>3240.5999999999999</v>
+      </c>
+      <c r="P161" s="5">
+        <v>3240.5999999999999</v>
+      </c>
+      <c r="Q161" s="6">
+        <v>0.19034675286511904</v>
+      </c>
+      <c r="R161" s="7">
+        <v>41</v>
+      </c>
+      <c r="S161" s="6">
+        <v>-0.023809523809523836</v>
+      </c>
+      <c r="T161" s="6">
+        <v>-0.086792569277294326</v>
+      </c>
+      <c r="U161" s="6">
+        <v>-0.39193976424118987</v>
+      </c>
+      <c r="V161" s="6">
+        <v>0.032874004813923344</v>
+      </c>
+      <c r="W161" s="6">
+        <v>-0.014743720298710116</v>
+      </c>
       <c r="X161" s="8"/>
       <c r="Y161" s="6"/>
       <c r="Z161" s="6"/>
-      <c r="AA161" s="8"/>
+      <c r="AA161" s="8">
+        <v>7.9070824999999996</v>
+      </c>
       <c r="AB161" s="8"/>
       <c r="AC161" s="8"/>
       <c r="AD161" s="8"/>
       <c r="AE161" s="6"/>
       <c r="AF161" s="9"/>
-      <c r="AG161" s="5"/>
+      <c r="AG161" s="5">
+        <v>-587.20000000000005</v>
+      </c>
       <c r="AH161" s="10">
         <v>5</v>
       </c>
@@ -23807,7 +24011,9 @@
       <c r="AB179" s="8">
         <v>3.2804347826086957</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>7.038405</v>
+      </c>
       <c r="AD179" s="8">
         <v>13.958695652173914</v>
       </c>
